--- a/data/10_summary.xlsx
+++ b/data/10_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haris\Documents\GitHub\MLpFEM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E7A154-A61F-41AC-8773-32AC24E48695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA74FB-3045-49F7-BFFB-D3EFBA3DEE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>Parameter</t>
   </si>
@@ -107,20 +107,29 @@
     <t>ML</t>
   </si>
   <si>
-    <t>min</t>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="CMU Serif"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -284,75 +293,83 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{99D73C8C-0986-48C5-B759-9D4ABAF3468B}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{C5ECA4AD-E0FF-4532-B6A4-722DFD76A3AE}"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{2C86391D-DE54-4246-8B1D-621A2196C0F8}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -685,16 +702,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8D671A-7B80-4EB9-BB8A-9E112AFFE017}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" customWidth="1"/>
-    <col min="4" max="7" width="33.28515625" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="33.28515625" customWidth="1"/>
+    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -716,11 +733,14 @@
       <c r="G1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -742,11 +762,14 @@
       <c r="G2" s="23">
         <v>20000</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="25">
+        <v>16000</v>
+      </c>
+      <c r="I2" s="13">
         <v>20942.565999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -768,11 +791,14 @@
       <c r="G3" s="23">
         <v>17500</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="25">
+        <v>24300</v>
+      </c>
+      <c r="I3" s="13">
         <v>21974.793000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -794,11 +820,14 @@
       <c r="G4" s="23">
         <v>70000</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="25">
+        <v>90000</v>
+      </c>
+      <c r="I4" s="13">
         <v>100402.273</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -820,11 +849,14 @@
       <c r="G5" s="23">
         <v>36</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="25">
+        <v>37</v>
+      </c>
+      <c r="I5" s="13">
         <v>36.171999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -846,11 +878,14 @@
       <c r="G6" s="23">
         <v>2</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -872,11 +907,14 @@
       <c r="G7" s="23">
         <v>10</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="25">
+        <v>7</v>
+      </c>
+      <c r="I7" s="13">
         <v>7.343</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -898,11 +936,14 @@
       <c r="G8" s="23">
         <v>0.5</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="I8" s="13">
         <v>0.68400000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -924,11 +965,14 @@
       <c r="G9" s="23">
         <v>0.2</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="13">
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -950,11 +994,14 @@
       <c r="G10" s="23">
         <v>0.9</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="13">
         <v>0.93400000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -976,11 +1023,14 @@
       <c r="G11" s="23">
         <v>0.41220000000000001</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="I11" s="13">
         <v>0.40899999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
@@ -1002,16 +1052,19 @@
       <c r="G12" s="24">
         <v>100</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="26">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I12" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="22">
         <v>1.5</v>
@@ -1029,25 +1082,32 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="H13" s="22">
+        <v>1.25</v>
+      </c>
+      <c r="I13" s="22">
         <f>20/60/60</f>
         <v>5.5555555555555549E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="17" spans="6:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="H15" s="1"/>
+    </row>
+    <row r="17" spans="6:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/10_summary.xlsx
+++ b/data/10_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haris\Documents\GitHub\MLpFEM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA74FB-3045-49F7-BFFB-D3EFBA3DEE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACFEEDE-C9EC-4638-99DE-91A522CE9DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -766,7 +766,7 @@
         <v>16000</v>
       </c>
       <c r="I2" s="13">
-        <v>20942.565999999999</v>
+        <v>20972.495999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -795,7 +795,7 @@
         <v>24300</v>
       </c>
       <c r="I3" s="13">
-        <v>21974.793000000001</v>
+        <v>21656.675999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -824,7 +824,7 @@
         <v>90000</v>
       </c>
       <c r="I4" s="13">
-        <v>100402.273</v>
+        <v>107278.656</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
         <v>37</v>
       </c>
       <c r="I5" s="13">
-        <v>36.171999999999997</v>
+        <v>37.423000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="I7" s="13">
-        <v>7.343</v>
+        <v>7.5940000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -940,7 +940,7 @@
         <v>0.9</v>
       </c>
       <c r="I8" s="13">
-        <v>0.68400000000000005</v>
+        <v>0.67700000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -969,7 +969,7 @@
         <v>0.2</v>
       </c>
       <c r="I9" s="13">
-        <v>0.11799999999999999</v>
+        <v>9.4E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -998,7 +998,7 @@
         <v>0.9</v>
       </c>
       <c r="I10" s="13">
-        <v>0.93400000000000005</v>
+        <v>0.95199999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1027,7 +1027,7 @@
         <v>0.4</v>
       </c>
       <c r="I11" s="13">
-        <v>0.40899999999999997</v>
+        <v>0.40799999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/data/10_summary.xlsx
+++ b/data/10_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haris\Documents\GitHub\MLpFEM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACFEEDE-C9EC-4638-99DE-91A522CE9DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58609A17-BD0A-44BB-8ABB-EA83870B06F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
+    <workbookView xWindow="32310" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1085,8 +1085,7 @@
         <v>1.25</v>
       </c>
       <c r="I13" s="22">
-        <f>20/60/60</f>
-        <v>5.5555555555555549E-3</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">

--- a/data/10_summary.xlsx
+++ b/data/10_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haris\Documents\GitHub\MLpFEM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58609A17-BD0A-44BB-8ABB-EA83870B06F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF0CCD8-E972-4BB1-B15C-E95267DEF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32310" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{624696BE-5913-4CAB-A232-561706B5FD5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Parameter</t>
   </si>
@@ -86,31 +86,34 @@
     <t>pref</t>
   </si>
   <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
     <t>ML</t>
   </si>
   <si>
-    <t>P6</t>
-  </si>
-  <si>
     <t>h</t>
+  </si>
+  <si>
+    <t>IA 3</t>
+  </si>
+  <si>
+    <t>EPD1</t>
+  </si>
+  <si>
+    <t>EPP2</t>
+  </si>
+  <si>
+    <t>EPD3</t>
+  </si>
+  <si>
+    <t>EPD4</t>
+  </si>
+  <si>
+    <t>EPD5</t>
+  </si>
+  <si>
+    <t>EPD6</t>
   </si>
 </sst>
 </file>
@@ -702,16 +705,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8D671A-7B80-4EB9-BB8A-9E112AFFE017}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" customWidth="1"/>
-    <col min="4" max="8" width="33.28515625" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="33.28515625" customWidth="1"/>
+    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -719,28 +722,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -765,11 +771,14 @@
       <c r="H2" s="25">
         <v>16000</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="25">
+        <v>16580</v>
+      </c>
+      <c r="J2" s="13">
         <v>20972.495999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -794,11 +803,14 @@
       <c r="H3" s="25">
         <v>24300</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="25">
+        <v>28410</v>
+      </c>
+      <c r="J3" s="13">
         <v>21656.675999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -823,11 +835,14 @@
       <c r="H4" s="25">
         <v>90000</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="25">
+        <v>77770</v>
+      </c>
+      <c r="J4" s="13">
         <v>107278.656</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -852,11 +867,14 @@
       <c r="H5" s="25">
         <v>37</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="25">
+        <v>36.04</v>
+      </c>
+      <c r="J5" s="13">
         <v>37.423000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -881,11 +899,14 @@
       <c r="H6" s="25">
         <v>0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -910,11 +931,14 @@
       <c r="H7" s="25">
         <v>7</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="25">
+        <v>6.04</v>
+      </c>
+      <c r="J7" s="13">
         <v>7.5940000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -939,11 +963,14 @@
       <c r="H8" s="25">
         <v>0.9</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="25">
+        <v>0.99580000000000002</v>
+      </c>
+      <c r="J8" s="13">
         <v>0.67700000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -968,11 +995,14 @@
       <c r="H9" s="25">
         <v>0.2</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="J9" s="13">
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -997,11 +1027,14 @@
       <c r="H10" s="25">
         <v>0.9</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="J10" s="13">
         <v>0.95199999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -1026,11 +1059,14 @@
       <c r="H11" s="25">
         <v>0.4</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="25">
+        <v>0.41170000000000001</v>
+      </c>
+      <c r="J11" s="13">
         <v>0.40799999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
@@ -1055,16 +1091,19 @@
       <c r="H12" s="26">
         <v>100</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="26">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J12" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13" s="22">
         <v>1.5</v>
@@ -1085,28 +1124,35 @@
         <v>1.25</v>
       </c>
       <c r="I13" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="J13" s="22">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="17" spans="6:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="17" spans="6:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-    </row>
-    <row r="19" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="19" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
-    </row>
-    <row r="20" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="20"/>
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
